--- a/research/traditional_assets/database/data/philippines/philippines_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_reinsurance.xlsx
@@ -588,28 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.246</v>
-      </c>
-      <c r="E2">
-        <v>0.508</v>
+        <v>0.04019999999999999</v>
       </c>
       <c r="G2">
-        <v>0.0651535380507343</v>
+        <v>0.07116182572614108</v>
       </c>
       <c r="H2">
-        <v>0.0651535380507343</v>
+        <v>0.07116182572614108</v>
       </c>
       <c r="I2">
-        <v>0.09418627843060046</v>
+        <v>-0.08697262467281855</v>
       </c>
       <c r="J2">
-        <v>0.08709803273427692</v>
+        <v>-0.08697262467281855</v>
       </c>
       <c r="K2">
-        <v>7.18</v>
+        <v>-4.69</v>
       </c>
       <c r="L2">
-        <v>0.09586114819759678</v>
+        <v>-0.09730290456431535</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -618,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,61 +624,61 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="V2">
-        <v>0.8016194331983806</v>
+        <v>0.8914027149321266</v>
       </c>
       <c r="W2">
-        <v>0.06216450216450217</v>
+        <v>-0.04110429447852761</v>
       </c>
       <c r="X2">
-        <v>0.09995011350569215</v>
+        <v>0.1395232212584626</v>
       </c>
       <c r="Y2">
-        <v>-0.03778561134118998</v>
+        <v>-0.1806275157369902</v>
       </c>
       <c r="Z2">
-        <v>0.7677544073282837</v>
+        <v>0.5109482723062789</v>
       </c>
       <c r="AA2">
-        <v>0.06686989850136422</v>
+        <v>-0.04443851231451908</v>
       </c>
       <c r="AB2">
-        <v>0.09986291002526862</v>
+        <v>0.1394268051173742</v>
       </c>
       <c r="AC2">
-        <v>-0.03299301152390439</v>
+        <v>-0.1838653174318933</v>
       </c>
       <c r="AD2">
-        <v>0.014</v>
+        <v>0.006</v>
       </c>
       <c r="AE2">
-        <v>0.01723872774012753</v>
+        <v>0.02040254614927466</v>
       </c>
       <c r="AF2">
-        <v>0.03123872774012754</v>
+        <v>0.02640254614927465</v>
       </c>
       <c r="AG2">
-        <v>-19.76876127225987</v>
+        <v>-19.67359745385073</v>
       </c>
       <c r="AH2">
-        <v>0.001263128308453397</v>
+        <v>0.00119325977615234</v>
       </c>
       <c r="AI2">
-        <v>0.0002737088293122575</v>
+        <v>0.0002916557535335059</v>
       </c>
       <c r="AJ2">
-        <v>-4.008883439581406</v>
+        <v>-8.108134194415889</v>
       </c>
       <c r="AK2">
-        <v>-0.2095674936413874</v>
+        <v>-0.2777720842313253</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -690,10 +687,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>0.001961333706920706</v>
+        <v>-0.001460564751703992</v>
       </c>
       <c r="AP2">
-        <v>-2.769509844810853</v>
+        <v>4.789093830051296</v>
       </c>
     </row>
     <row r="3">
@@ -713,28 +710,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.246</v>
-      </c>
-      <c r="E3">
-        <v>0.508</v>
+        <v>0.04019999999999999</v>
       </c>
       <c r="G3">
-        <v>0.0651535380507343</v>
+        <v>0.07116182572614108</v>
       </c>
       <c r="H3">
-        <v>0.0651535380507343</v>
+        <v>0.07116182572614108</v>
       </c>
       <c r="I3">
-        <v>0.09418627843060046</v>
+        <v>-0.08697262467281855</v>
       </c>
       <c r="J3">
-        <v>0.08709803273427692</v>
+        <v>-0.08697262467281855</v>
       </c>
       <c r="K3">
-        <v>7.18</v>
+        <v>-4.69</v>
       </c>
       <c r="L3">
-        <v>0.09586114819759678</v>
+        <v>-0.09730290456431535</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +737,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,61 +746,61 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="V3">
-        <v>0.8016194331983806</v>
+        <v>0.8914027149321266</v>
       </c>
       <c r="W3">
-        <v>0.06216450216450217</v>
+        <v>-0.04110429447852761</v>
       </c>
       <c r="X3">
-        <v>0.09995011350569215</v>
+        <v>0.1395232212584626</v>
       </c>
       <c r="Y3">
-        <v>-0.03778561134118998</v>
+        <v>-0.1806275157369902</v>
       </c>
       <c r="Z3">
-        <v>0.7677544073282837</v>
+        <v>0.5109482723062789</v>
       </c>
       <c r="AA3">
-        <v>0.06686989850136422</v>
+        <v>-0.04443851231451908</v>
       </c>
       <c r="AB3">
-        <v>0.09986291002526862</v>
+        <v>0.1394268051173742</v>
       </c>
       <c r="AC3">
-        <v>-0.03299301152390439</v>
+        <v>-0.1838653174318933</v>
       </c>
       <c r="AD3">
-        <v>0.014</v>
+        <v>0.006</v>
       </c>
       <c r="AE3">
-        <v>0.01723872774012753</v>
+        <v>0.02040254614927466</v>
       </c>
       <c r="AF3">
-        <v>0.03123872774012754</v>
+        <v>0.02640254614927465</v>
       </c>
       <c r="AG3">
-        <v>-19.76876127225987</v>
+        <v>-19.67359745385073</v>
       </c>
       <c r="AH3">
-        <v>0.001263128308453397</v>
+        <v>0.00119325977615234</v>
       </c>
       <c r="AI3">
-        <v>0.0002737088293122575</v>
+        <v>0.0002916557535335059</v>
       </c>
       <c r="AJ3">
-        <v>-4.008883439581406</v>
+        <v>-8.108134194415889</v>
       </c>
       <c r="AK3">
-        <v>-0.2095674936413874</v>
+        <v>-0.2777720842313253</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -815,10 +809,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.001961333706920706</v>
+        <v>-0.001460564751703992</v>
       </c>
       <c r="AP3">
-        <v>-2.769509844810853</v>
+        <v>4.789093830051296</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/philippines/philippines_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_reinsurance.xlsx
@@ -588,25 +588,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.04019999999999999</v>
+        <v>0.06660000000000001</v>
+      </c>
+      <c r="E2">
+        <v>0.318</v>
       </c>
       <c r="G2">
-        <v>0.07116182572614108</v>
+        <v>0.02988668555240793</v>
       </c>
       <c r="H2">
-        <v>0.07116182572614108</v>
+        <v>0.02988668555240793</v>
       </c>
       <c r="I2">
-        <v>-0.08697262467281855</v>
+        <v>0.1247034959552531</v>
       </c>
       <c r="J2">
-        <v>-0.08697262467281855</v>
+        <v>0.1048293136593542</v>
       </c>
       <c r="K2">
-        <v>-4.69</v>
+        <v>7.49</v>
       </c>
       <c r="L2">
-        <v>-0.09730290456431535</v>
+        <v>0.1060906515580737</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,73 +627,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>19.7</v>
+        <v>9.44</v>
       </c>
       <c r="V2">
-        <v>0.8914027149321266</v>
+        <v>0.6378378378378378</v>
       </c>
       <c r="W2">
-        <v>-0.04110429447852761</v>
+        <v>0.08276243093922653</v>
       </c>
       <c r="X2">
-        <v>0.1395232212584626</v>
+        <v>0.117872615640291</v>
       </c>
       <c r="Y2">
-        <v>-0.1806275157369902</v>
+        <v>-0.03511018470106447</v>
       </c>
       <c r="Z2">
-        <v>0.5109482723062789</v>
+        <v>0.997024940734063</v>
       </c>
       <c r="AA2">
-        <v>-0.04443851231451908</v>
+        <v>0.1045174402384101</v>
       </c>
       <c r="AB2">
-        <v>0.1394268051173742</v>
+        <v>0.117852390195025</v>
       </c>
       <c r="AC2">
-        <v>-0.1838653174318933</v>
+        <v>-0.0133349499566149</v>
       </c>
       <c r="AD2">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>0.02040254614927466</v>
+        <v>0.004665927795654732</v>
       </c>
       <c r="AF2">
-        <v>0.02640254614927465</v>
+        <v>0.004665927795654732</v>
       </c>
       <c r="AG2">
-        <v>-19.67359745385073</v>
+        <v>-9.435334072204345</v>
       </c>
       <c r="AH2">
-        <v>0.00119325977615234</v>
+        <v>0.0003151660306562194</v>
       </c>
       <c r="AI2">
-        <v>0.0002916557535335059</v>
+        <v>4.534223743487627e-05</v>
       </c>
       <c r="AJ2">
-        <v>-8.108134194415889</v>
+        <v>-1.758792476399612</v>
       </c>
       <c r="AK2">
-        <v>-0.2777720842313253</v>
+        <v>-0.1009508136421675</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AN2">
-        <v>-0.001460564751703992</v>
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>4400</v>
       </c>
       <c r="AP2">
-        <v>4.789093830051296</v>
+        <v>-1.061939681733747</v>
+      </c>
+      <c r="AQ2">
+        <v>4400</v>
       </c>
     </row>
     <row r="3">
@@ -710,25 +719,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.04019999999999999</v>
+        <v>0.06660000000000001</v>
+      </c>
+      <c r="E3">
+        <v>0.318</v>
       </c>
       <c r="G3">
-        <v>0.07116182572614108</v>
+        <v>0.02988668555240793</v>
       </c>
       <c r="H3">
-        <v>0.07116182572614108</v>
+        <v>0.02988668555240793</v>
       </c>
       <c r="I3">
-        <v>-0.08697262467281855</v>
+        <v>0.1247034959552531</v>
       </c>
       <c r="J3">
-        <v>-0.08697262467281855</v>
+        <v>0.1048293136593542</v>
       </c>
       <c r="K3">
-        <v>-4.69</v>
+        <v>7.49</v>
       </c>
       <c r="L3">
-        <v>-0.09730290456431535</v>
+        <v>0.1060906515580737</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -737,7 +749,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -746,73 +758,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>19.7</v>
+        <v>9.44</v>
       </c>
       <c r="V3">
-        <v>0.8914027149321266</v>
+        <v>0.6378378378378378</v>
       </c>
       <c r="W3">
-        <v>-0.04110429447852761</v>
+        <v>0.08276243093922653</v>
       </c>
       <c r="X3">
-        <v>0.1395232212584626</v>
+        <v>0.117872615640291</v>
       </c>
       <c r="Y3">
-        <v>-0.1806275157369902</v>
+        <v>-0.03511018470106447</v>
       </c>
       <c r="Z3">
-        <v>0.5109482723062789</v>
+        <v>0.997024940734063</v>
       </c>
       <c r="AA3">
-        <v>-0.04443851231451908</v>
+        <v>0.1045174402384101</v>
       </c>
       <c r="AB3">
-        <v>0.1394268051173742</v>
+        <v>0.117852390195025</v>
       </c>
       <c r="AC3">
-        <v>-0.1838653174318933</v>
+        <v>-0.0133349499566149</v>
       </c>
       <c r="AD3">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>0.02040254614927466</v>
+        <v>0.004665927795654732</v>
       </c>
       <c r="AF3">
-        <v>0.02640254614927465</v>
+        <v>0.004665927795654732</v>
       </c>
       <c r="AG3">
-        <v>-19.67359745385073</v>
+        <v>-9.435334072204345</v>
       </c>
       <c r="AH3">
-        <v>0.00119325977615234</v>
+        <v>0.0003151660306562194</v>
       </c>
       <c r="AI3">
-        <v>0.0002916557535335059</v>
+        <v>4.534223743487627e-05</v>
       </c>
       <c r="AJ3">
-        <v>-8.108134194415889</v>
+        <v>-1.758792476399612</v>
       </c>
       <c r="AK3">
-        <v>-0.2777720842313253</v>
+        <v>-0.1009508136421675</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AN3">
-        <v>-0.001460564751703992</v>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>4400</v>
       </c>
       <c r="AP3">
-        <v>4.789093830051296</v>
+        <v>-1.061939681733747</v>
+      </c>
+      <c r="AQ3">
+        <v>4400</v>
       </c>
     </row>
   </sheetData>
